--- a/employment_forms/042_work_trial_agreement_confirmation--employment_forms.xlsx
+++ b/employment_forms/042_work_trial_agreement_confirmation--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed Recruiter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed Hrs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed Employment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>consent_to_terms_choices</t>
+          <t>participant_signatures_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hr_signature_choices</t>
+          <t>recruiter_signature_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,97 +1267,148 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employment_program_signature_choices</t>
+          <t>hr_signature_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>employment_program_signature_choices</t>
+          <t>hr_signature_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participant_status_choices</t>
+          <t>employment_program_signature_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_status_choices</t>
+          <t>employment_program_signature_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>employment_program_signature_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>participant_status_choices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option3</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>participant_status_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>participant_status_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
